--- a/documentation/er_diagram.xlsx
+++ b/documentation/er_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ralfs_cviklinskis_postsite\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386DE53-06DE-4A12-8B07-574EFC327CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A5669-AF14-4227-BFEC-54E072FAD3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{49328A8C-EE67-427F-A201-2444A472A0A4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -115,6 +115,24 @@
   </si>
   <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>comment_account_id</t>
+  </si>
+  <si>
+    <t>post_account_id</t>
+  </si>
+  <si>
+    <t>post_id</t>
+  </si>
+  <si>
+    <t>varchar(1000)</t>
+  </si>
+  <si>
+    <t>varchar(50)</t>
   </si>
 </sst>
 </file>
@@ -200,18 +218,18 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -319,8 +337,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="1600200" y="3939536"/>
-          <a:ext cx="388620" cy="548644"/>
+          <a:off x="3849272" y="1916133"/>
+          <a:ext cx="425548" cy="545127"/>
         </a:xfrm>
         <a:prstGeom prst="rightBracket">
           <a:avLst/>
@@ -390,6 +408,283 @@
         <a:ln>
           <a:tailEnd type="triangle"/>
         </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>325315</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>111370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>103160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Right Bracket 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B135624-1676-4ED9-BB4C-0EECFEA1AB4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1626577" y="474785"/>
+          <a:ext cx="359898" cy="2535698"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBracket">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="arrow" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="lv-LV" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>313592</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>105508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>673490</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>103159</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Right Bracket 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55EF4C29-06D3-462F-AD3D-3A9F8295E457}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1614854" y="468923"/>
+          <a:ext cx="359898" cy="2723267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBracket">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="arrow" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="lv-LV" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>205154</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>105104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>704193</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>140677</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Straight Arrow Connector 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAC75111-4BDB-4BD5-AD22-8863AABB1218}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3757651" y="472966"/>
+          <a:ext cx="499039" cy="35573"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>211016</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>140677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>211016</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>87924</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Straight Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274E6D2E-A199-40AE-BD1F-5B45DC7AF923}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3763108" y="504092"/>
+          <a:ext cx="0" cy="2854570"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>823912</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCBF7E4E-1560-40FB-A87A-0A86104FA87E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3543300" y="3333750"/>
+          <a:ext cx="204788" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="3">
@@ -723,15 +1018,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="7"/>
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="K2" s="5"/>
+      <c r="H2" s="6"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
@@ -746,7 +1041,7 @@
       <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D4" s="1" t="s">
@@ -761,7 +1056,7 @@
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D5" s="1" t="s">
@@ -776,7 +1071,7 @@
       <c r="H5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D6" s="1" t="s">
@@ -791,22 +1086,22 @@
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="4:18" x14ac:dyDescent="0.3">
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>31</v>
+      </c>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="4:18" x14ac:dyDescent="0.3">
       <c r="G8" s="1" t="s">
@@ -815,7 +1110,7 @@
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="2"/>
       <c r="O8" s="1" t="s">
         <v>11</v>
       </c>
@@ -830,17 +1125,17 @@
       </c>
     </row>
     <row r="9" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="7"/>
       <c r="G9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="2"/>
       <c r="O9" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,7 +1162,7 @@
       <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="2"/>
       <c r="O10" s="1" t="s">
         <v>11</v>
       </c>
@@ -894,7 +1189,7 @@
       <c r="H11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="2"/>
       <c r="O11" s="1" t="s">
         <v>5</v>
       </c>
@@ -915,35 +1210,35 @@
       <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="2"/>
       <c r="O12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" s="6" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="4:18" x14ac:dyDescent="0.3">
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="6"/>
       <c r="O13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R13" s="6" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -960,24 +1255,28 @@
       <c r="P14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R14" s="6" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="7"/>
       <c r="G15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="4"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1" t="s">
         <v>7</v>
@@ -985,14 +1284,18 @@
       <c r="P15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R15" s="6" t="s">
+      <c r="Q15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="L16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,14 +1309,20 @@
       <c r="P16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="Q16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,35 +1336,54 @@
       <c r="P17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="12:18" x14ac:dyDescent="0.3">
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
+      <c r="Q17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
